--- a/frotas_manutencoes.xlsx
+++ b/frotas_manutencoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,133 +470,6 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>status_manutencao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Corretiva</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Remendo De Pneu</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Borracharia São Matheus</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Executada</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Troca De Oleo</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Programada</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SIN4I57</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Preventiva</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Troca De Amortecedor</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Programada</t>
         </is>
       </c>
     </row>

--- a/frotas_manutencoes.xlsx
+++ b/frotas_manutencoes.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,63 +425,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>placa</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>tipo_manutencao</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>km</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>servico_executado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fornecedor</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>manutencao_agendada</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>proxima_revisao</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>status_manutencao</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>responsavel_lancamento</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>registrado_em</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>nota_anexo</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>status_conferencia</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>observacao_administrativo</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>observacoes</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>manutencao_agendada</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>status_manutencao</t>
         </is>
       </c>
     </row>
